--- a/out/Attention-Mamba1_repeat_4_000005.xlsx
+++ b/out/Attention-Mamba1_repeat_4_000005.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.6660834373006792</v>
+        <v>1.473179781458245</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.6660834373006792</v>
+        <v>1.473179781458245</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.6660834373006792</v>
+        <v>2.073179781458245</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.6660834373006792</v>
+        <v>2.073179781458245</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.6660834373006792</v>
+        <v>2.073179781458245</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.6660834373006792</v>
+        <v>2.073179781458245</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7297,14 +7297,14 @@
       </c>
       <c r="IZ8" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.6660834373006792</v>
+        <v>2.073179781458245</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.6660834373006792</v>
+        <v>2.073179781458245</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.6660834373006792</v>
+        <v>2.073179781458245</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9682,14 +9682,14 @@
       </c>
       <c r="IZ11" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.6660834373006792</v>
+        <v>1.473179781458245</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10477,14 +10477,14 @@
       </c>
       <c r="IZ12" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.6660834373006792</v>
+        <v>1.473179781458245</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11272,14 +11272,14 @@
       </c>
       <c r="IZ13" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.6660834373006792</v>
+        <v>1.473179781458245</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.6660834373006792</v>
+        <v>1.473179781458245</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.6660834373006792</v>
+        <v>2.073179781458245</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.6660834373006792</v>
+        <v>2.073179781458245</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>5.653970270522433</v>
+        <v>2.073179781458245</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.06608343730067928</v>
+        <v>2.073179781458245</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.06608343730067928</v>
+        <v>2.073179781458245</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.6660834373006792</v>
+        <v>2.073179781458245</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.6660834373006792</v>
+        <v>2.073179781458245</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.6660834373006792</v>
+        <v>2.073179781458245</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.6660834373006792</v>
+        <v>1.473179781458245</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.6660834373006792</v>
+        <v>1.473179781458245</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.6660834373006792</v>
+        <v>1.473179781458245</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.6660834373006792</v>
+        <v>1.473179781458245</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.6660834373006792</v>
+        <v>1.473179781458245</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>5.653970270522433</v>
+        <v>1.473179781458245</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.06608343730067928</v>
+        <v>1.473179781458245</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.06608343730067928</v>
+        <v>1.473179781458245</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.6660834373006792</v>
+        <v>1.473179781458245</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.6660834373006792</v>
+        <v>1.473179781458245</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.6660834373006792</v>
+        <v>1.473179781458245</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.6660834373006792</v>
+        <v>1.473179781458245</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.6660834373006792</v>
+        <v>1.473179781458245</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.6660834373006792</v>
+        <v>1.473179781458245</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.6660834373006792</v>
+        <v>1.473179781458245</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34327,14 +34327,14 @@
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.6660834373006792</v>
+        <v>1.473179781458245</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35122,14 +35122,14 @@
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.6660834373006792</v>
+        <v>1.473179781458245</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,7 +35924,7 @@
         <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36712,14 +36712,14 @@
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.6660834373006792</v>
+        <v>1.473179781458245</v>
       </c>
       <c r="JC45" t="n">
         <v>0</v>
@@ -37514,7 +37514,7 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC46" t="n">
         <v>0</v>
@@ -38309,7 +38309,7 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC47" t="n">
         <v>0</v>
@@ -39097,14 +39097,14 @@
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.6660834373006792</v>
+        <v>1.473179781458245</v>
       </c>
       <c r="JC48" t="n">
         <v>0</v>
@@ -39899,7 +39899,7 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC49" t="n">
         <v>0</v>
@@ -40694,7 +40694,7 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC50" t="n">
         <v>0</v>
@@ -41489,7 +41489,7 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC51" t="n">
         <v>0</v>
@@ -42284,7 +42284,7 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC52" t="n">
         <v>0</v>
@@ -43079,7 +43079,7 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC53" t="n">
         <v>0</v>
@@ -43874,7 +43874,7 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC54" t="n">
         <v>0</v>
@@ -44662,14 +44662,14 @@
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.6660834373006792</v>
+        <v>2.073179781458245</v>
       </c>
       <c r="JC55" t="n">
         <v>0</v>
@@ -45457,14 +45457,14 @@
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.6660834373006792</v>
+        <v>2.073179781458245</v>
       </c>
       <c r="JC56" t="n">
         <v>0</v>
@@ -46252,14 +46252,14 @@
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.6660834373006792</v>
+        <v>2.073179781458245</v>
       </c>
       <c r="JC57" t="n">
         <v>0</v>
@@ -47047,14 +47047,14 @@
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.6660834373006792</v>
+        <v>2.073179781458245</v>
       </c>
       <c r="JC58" t="n">
         <v>0</v>
@@ -47842,14 +47842,14 @@
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.6660834373006792</v>
+        <v>2.073179781458245</v>
       </c>
       <c r="JC59" t="n">
         <v>0</v>
@@ -48637,14 +48637,14 @@
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.6660834373006792</v>
+        <v>2.073179781458245</v>
       </c>
       <c r="JC60" t="n">
         <v>0</v>
@@ -49432,14 +49432,14 @@
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.6660834373006792</v>
+        <v>2.073179781458245</v>
       </c>
       <c r="JC61" t="n">
         <v>0</v>
@@ -50227,14 +50227,14 @@
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.6660834373006792</v>
+        <v>2.073179781458245</v>
       </c>
       <c r="JC62" t="n">
         <v>0</v>
@@ -51029,7 +51029,7 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC63" t="n">
         <v>0</v>
@@ -51824,7 +51824,7 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC64" t="n">
         <v>0</v>
@@ -52619,7 +52619,7 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC65" t="n">
         <v>0</v>
@@ -53414,7 +53414,7 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC66" t="n">
         <v>0</v>
@@ -54209,7 +54209,7 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC67" t="n">
         <v>0</v>
@@ -55004,7 +55004,7 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC68" t="n">
         <v>0</v>
@@ -55799,7 +55799,7 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC69" t="n">
         <v>0</v>
@@ -56594,7 +56594,7 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC70" t="n">
         <v>0</v>
@@ -57389,7 +57389,7 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC71" t="n">
         <v>0</v>
@@ -58184,7 +58184,7 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC72" t="n">
         <v>0</v>
@@ -58979,7 +58979,7 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC73" t="n">
         <v>0</v>
@@ -59767,14 +59767,14 @@
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>5.653970270522433</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC74" t="n">
         <v>0</v>
@@ -60562,14 +60562,14 @@
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA75" t="n">
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.06608343730067928</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC75" t="n">
         <v>0</v>
@@ -61357,14 +61357,14 @@
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>5.653970270522433</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC76" t="n">
         <v>0</v>
@@ -62152,14 +62152,14 @@
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA77" t="n">
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.06608343730067928</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC77" t="n">
         <v>0</v>
@@ -62947,14 +62947,14 @@
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA78" t="n">
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.06608343730067928</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC78" t="n">
         <v>0</v>
@@ -63749,7 +63749,7 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC79" t="n">
         <v>0</v>
@@ -64544,7 +64544,7 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC80" t="n">
         <v>0</v>
@@ -65339,7 +65339,7 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC81" t="n">
         <v>0</v>
@@ -66134,7 +66134,7 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC82" t="n">
         <v>0</v>
@@ -66929,7 +66929,7 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC83" t="n">
         <v>0</v>
@@ -67724,7 +67724,7 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC84" t="n">
         <v>0</v>
@@ -68519,7 +68519,7 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC85" t="n">
         <v>0</v>
@@ -69314,7 +69314,7 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC86" t="n">
         <v>0</v>
@@ -70109,7 +70109,7 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC87" t="n">
         <v>0</v>
@@ -70904,7 +70904,7 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC88" t="n">
         <v>0</v>
@@ -71699,7 +71699,7 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC89" t="n">
         <v>0</v>
@@ -72494,7 +72494,7 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC90" t="n">
         <v>0</v>
@@ -73289,7 +73289,7 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC91" t="n">
         <v>0</v>
@@ -74084,7 +74084,7 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC92" t="n">
         <v>0</v>
@@ -74879,7 +74879,7 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC93" t="n">
         <v>0</v>
@@ -75674,7 +75674,7 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC94" t="n">
         <v>0</v>
@@ -76469,7 +76469,7 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC95" t="n">
         <v>0</v>
@@ -77264,7 +77264,7 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC96" t="n">
         <v>0</v>
@@ -78059,7 +78059,7 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC97" t="n">
         <v>0</v>
@@ -78854,7 +78854,7 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC98" t="n">
         <v>0</v>
@@ -79649,7 +79649,7 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC99" t="n">
         <v>0</v>
@@ -80444,7 +80444,7 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC100" t="n">
         <v>0</v>
@@ -81239,7 +81239,7 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC101" t="n">
         <v>0</v>
@@ -82034,7 +82034,7 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC102" t="n">
         <v>0</v>
@@ -82829,7 +82829,7 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC103" t="n">
         <v>0</v>
@@ -83624,7 +83624,7 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC104" t="n">
         <v>0</v>
@@ -84419,7 +84419,7 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC105" t="n">
         <v>0</v>
@@ -85214,7 +85214,7 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC106" t="n">
         <v>0</v>
@@ -86009,7 +86009,7 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC107" t="n">
         <v>0</v>
@@ -86804,7 +86804,7 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC108" t="n">
         <v>0</v>
@@ -87599,7 +87599,7 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC109" t="n">
         <v>0</v>
@@ -88394,7 +88394,7 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC110" t="n">
         <v>0</v>
@@ -89189,7 +89189,7 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC111" t="n">
         <v>0</v>
@@ -89984,7 +89984,7 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC112" t="n">
         <v>0</v>
@@ -90779,7 +90779,7 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC113" t="n">
         <v>0</v>
@@ -91567,14 +91567,14 @@
       </c>
       <c r="IZ114" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>5.653970270522433</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC114" t="n">
         <v>0</v>
@@ -92362,14 +92362,14 @@
       </c>
       <c r="IZ115" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA115" t="n">
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.06608343730067928</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC115" t="n">
         <v>0</v>
@@ -93157,14 +93157,14 @@
       </c>
       <c r="IZ116" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>5.653970270522433</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC116" t="n">
         <v>0</v>
@@ -93952,14 +93952,14 @@
       </c>
       <c r="IZ117" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA117" t="n">
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.06608343730067928</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC117" t="n">
         <v>0</v>
@@ -94747,14 +94747,14 @@
       </c>
       <c r="IZ118" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA118" t="n">
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.06608343730067928</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC118" t="n">
         <v>0</v>
@@ -95549,7 +95549,7 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC119" t="n">
         <v>0</v>
@@ -96344,7 +96344,7 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC120" t="n">
         <v>0</v>
@@ -97139,7 +97139,7 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC121" t="n">
         <v>0</v>
@@ -97927,14 +97927,14 @@
       </c>
       <c r="IZ122" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>5.653970270522433</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC122" t="n">
         <v>0</v>
@@ -98722,14 +98722,14 @@
       </c>
       <c r="IZ123" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA123" t="n">
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.06608343730067928</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC123" t="n">
         <v>0</v>
@@ -99517,14 +99517,14 @@
       </c>
       <c r="IZ124" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>5.653970270522433</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC124" t="n">
         <v>0</v>
@@ -100312,14 +100312,14 @@
       </c>
       <c r="IZ125" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA125" t="n">
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.06608343730067928</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC125" t="n">
         <v>0</v>
@@ -101107,14 +101107,14 @@
       </c>
       <c r="IZ126" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA126" t="n">
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.06608343730067928</v>
+        <v>-1.40535882480514</v>
       </c>
       <c r="JC126" t="n">
         <v>0</v>

--- a/out/Attention-Mamba1_repeat_4_000005.xlsx
+++ b/out/Attention-Mamba1_repeat_4_000005.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA6" t="n">
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA7" t="n">
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA9" t="n">
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA10" t="n">
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9682,14 +9682,14 @@
       </c>
       <c r="IZ11" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA11" t="n">
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10477,14 +10477,14 @@
       </c>
       <c r="IZ12" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA12" t="n">
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11272,14 +11272,14 @@
       </c>
       <c r="IZ13" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA13" t="n">
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA14" t="n">
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA15" t="n">
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA16" t="n">
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA17" t="n">
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA18" t="n">
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA19" t="n">
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA20" t="n">
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.6660834373006792</v>
+        <v>0.9526475715196895</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>5.653970270522433</v>
+        <v>0.9526475715196895</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.06608343730067928</v>
+        <v>0.9526475715196895</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA23" t="n">
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.06608343730067928</v>
+        <v>-0.09102864272046574</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.09102864272046574</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA25" t="n">
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA26" t="n">
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA27" t="n">
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA28" t="n">
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA29" t="n">
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA30" t="n">
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA31" t="n">
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.6660834373006792</v>
+        <v>0.9526475715196895</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>5.653970270522433</v>
+        <v>0.9526475715196895</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.06608343730067928</v>
+        <v>0.9526475715196895</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA34" t="n">
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.06608343730067928</v>
+        <v>-0.09102864272046574</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.09102864272046574</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA36" t="n">
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA37" t="n">
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA38" t="n">
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA39" t="n">
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA40" t="n">
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA41" t="n">
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34327,14 +34327,14 @@
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA42" t="n">
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35122,14 +35122,14 @@
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA43" t="n">
         <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35917,14 +35917,14 @@
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA44" t="n">
         <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36712,14 +36712,14 @@
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA45" t="n">
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC45" t="n">
         <v>0</v>
@@ -37507,14 +37507,14 @@
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA46" t="n">
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC46" t="n">
         <v>0</v>
@@ -38302,14 +38302,14 @@
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA47" t="n">
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC47" t="n">
         <v>0</v>
@@ -39097,14 +39097,14 @@
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA48" t="n">
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC48" t="n">
         <v>0</v>
@@ -39892,14 +39892,14 @@
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA49" t="n">
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC49" t="n">
         <v>0</v>
@@ -40687,14 +40687,14 @@
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA50" t="n">
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC50" t="n">
         <v>0</v>
@@ -41482,14 +41482,14 @@
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA51" t="n">
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC51" t="n">
         <v>0</v>
@@ -42277,14 +42277,14 @@
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA52" t="n">
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC52" t="n">
         <v>0</v>
@@ -43072,14 +43072,14 @@
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA53" t="n">
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC53" t="n">
         <v>0</v>
@@ -43867,14 +43867,14 @@
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA54" t="n">
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC54" t="n">
         <v>0</v>
@@ -44662,14 +44662,14 @@
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA55" t="n">
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC55" t="n">
         <v>0</v>
@@ -45457,14 +45457,14 @@
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA56" t="n">
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC56" t="n">
         <v>0</v>
@@ -46252,14 +46252,14 @@
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA57" t="n">
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC57" t="n">
         <v>0</v>
@@ -47047,14 +47047,14 @@
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA58" t="n">
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC58" t="n">
         <v>0</v>
@@ -47842,14 +47842,14 @@
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA59" t="n">
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC59" t="n">
         <v>0</v>
@@ -48637,14 +48637,14 @@
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA60" t="n">
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC60" t="n">
         <v>0</v>
@@ -49432,14 +49432,14 @@
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA61" t="n">
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC61" t="n">
         <v>0</v>
@@ -50227,14 +50227,14 @@
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA62" t="n">
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC62" t="n">
         <v>0</v>
@@ -51022,14 +51022,14 @@
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA63" t="n">
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC63" t="n">
         <v>0</v>
@@ -51817,14 +51817,14 @@
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA64" t="n">
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC64" t="n">
         <v>0</v>
@@ -52612,14 +52612,14 @@
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA65" t="n">
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC65" t="n">
         <v>0</v>
@@ -53407,14 +53407,14 @@
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA66" t="n">
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC66" t="n">
         <v>0</v>
@@ -54202,14 +54202,14 @@
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA67" t="n">
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC67" t="n">
         <v>0</v>
@@ -54997,14 +54997,14 @@
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA68" t="n">
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC68" t="n">
         <v>0</v>
@@ -55792,14 +55792,14 @@
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA69" t="n">
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC69" t="n">
         <v>0</v>
@@ -56587,14 +56587,14 @@
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA70" t="n">
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC70" t="n">
         <v>0</v>
@@ -57382,14 +57382,14 @@
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA71" t="n">
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC71" t="n">
         <v>0</v>
@@ -58177,14 +58177,14 @@
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA72" t="n">
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC72" t="n">
         <v>0</v>
@@ -58972,14 +58972,14 @@
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA73" t="n">
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.6660834373006792</v>
+        <v>0.9526475715196895</v>
       </c>
       <c r="JC73" t="n">
         <v>0</v>
@@ -59774,7 +59774,7 @@
         <v>1</v>
       </c>
       <c r="JB74" t="n">
-        <v>5.653970270522433</v>
+        <v>0.9526475715196895</v>
       </c>
       <c r="JC74" t="n">
         <v>0</v>
@@ -60569,7 +60569,7 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.06608343730067928</v>
+        <v>1.996323785759845</v>
       </c>
       <c r="JC75" t="n">
         <v>0</v>
@@ -61364,7 +61364,7 @@
         <v>1</v>
       </c>
       <c r="JB76" t="n">
-        <v>5.653970270522433</v>
+        <v>0.9526475715196895</v>
       </c>
       <c r="JC76" t="n">
         <v>0</v>
@@ -62159,7 +62159,7 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.06608343730067928</v>
+        <v>0.9526475715196895</v>
       </c>
       <c r="JC77" t="n">
         <v>0</v>
@@ -62947,14 +62947,14 @@
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA78" t="n">
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.06608343730067928</v>
+        <v>-0.09102864272046574</v>
       </c>
       <c r="JC78" t="n">
         <v>0</v>
@@ -63742,14 +63742,14 @@
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA79" t="n">
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC79" t="n">
         <v>0</v>
@@ -64537,14 +64537,14 @@
       </c>
       <c r="IZ80" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA80" t="n">
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC80" t="n">
         <v>0</v>
@@ -65332,14 +65332,14 @@
       </c>
       <c r="IZ81" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA81" t="n">
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC81" t="n">
         <v>0</v>
@@ -66127,14 +66127,14 @@
       </c>
       <c r="IZ82" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA82" t="n">
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC82" t="n">
         <v>0</v>
@@ -66922,14 +66922,14 @@
       </c>
       <c r="IZ83" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA83" t="n">
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC83" t="n">
         <v>0</v>
@@ -67717,14 +67717,14 @@
       </c>
       <c r="IZ84" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA84" t="n">
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC84" t="n">
         <v>0</v>
@@ -68512,14 +68512,14 @@
       </c>
       <c r="IZ85" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA85" t="n">
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC85" t="n">
         <v>0</v>
@@ -69307,14 +69307,14 @@
       </c>
       <c r="IZ86" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA86" t="n">
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC86" t="n">
         <v>0</v>
@@ -70102,14 +70102,14 @@
       </c>
       <c r="IZ87" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA87" t="n">
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC87" t="n">
         <v>0</v>
@@ -70897,14 +70897,14 @@
       </c>
       <c r="IZ88" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA88" t="n">
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC88" t="n">
         <v>0</v>
@@ -71692,14 +71692,14 @@
       </c>
       <c r="IZ89" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA89" t="n">
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC89" t="n">
         <v>0</v>
@@ -72487,14 +72487,14 @@
       </c>
       <c r="IZ90" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA90" t="n">
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC90" t="n">
         <v>0</v>
@@ -73282,14 +73282,14 @@
       </c>
       <c r="IZ91" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA91" t="n">
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC91" t="n">
         <v>0</v>
@@ -74077,14 +74077,14 @@
       </c>
       <c r="IZ92" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA92" t="n">
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC92" t="n">
         <v>0</v>
@@ -74872,14 +74872,14 @@
       </c>
       <c r="IZ93" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA93" t="n">
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC93" t="n">
         <v>0</v>
@@ -75667,14 +75667,14 @@
       </c>
       <c r="IZ94" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA94" t="n">
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC94" t="n">
         <v>0</v>
@@ -76462,14 +76462,14 @@
       </c>
       <c r="IZ95" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA95" t="n">
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC95" t="n">
         <v>0</v>
@@ -77257,14 +77257,14 @@
       </c>
       <c r="IZ96" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA96" t="n">
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC96" t="n">
         <v>0</v>
@@ -78052,14 +78052,14 @@
       </c>
       <c r="IZ97" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA97" t="n">
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC97" t="n">
         <v>0</v>
@@ -78847,14 +78847,14 @@
       </c>
       <c r="IZ98" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA98" t="n">
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC98" t="n">
         <v>0</v>
@@ -79642,14 +79642,14 @@
       </c>
       <c r="IZ99" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA99" t="n">
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC99" t="n">
         <v>0</v>
@@ -80437,14 +80437,14 @@
       </c>
       <c r="IZ100" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA100" t="n">
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC100" t="n">
         <v>0</v>
@@ -81239,7 +81239,7 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC101" t="n">
         <v>0</v>
@@ -82034,7 +82034,7 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC102" t="n">
         <v>0</v>
@@ -82829,7 +82829,7 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC103" t="n">
         <v>0</v>
@@ -83624,7 +83624,7 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC104" t="n">
         <v>0</v>
@@ -84419,7 +84419,7 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC105" t="n">
         <v>0</v>
@@ -85214,7 +85214,7 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC106" t="n">
         <v>0</v>
@@ -86009,7 +86009,7 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC107" t="n">
         <v>0</v>
@@ -86804,7 +86804,7 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC108" t="n">
         <v>0</v>
@@ -87599,7 +87599,7 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC109" t="n">
         <v>0</v>
@@ -88394,7 +88394,7 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC110" t="n">
         <v>0</v>
@@ -89189,7 +89189,7 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC111" t="n">
         <v>0</v>
@@ -89984,7 +89984,7 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC112" t="n">
         <v>0</v>
@@ -90772,14 +90772,14 @@
       </c>
       <c r="IZ113" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA113" t="n">
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.6660834373006792</v>
+        <v>0.9526475715196895</v>
       </c>
       <c r="JC113" t="n">
         <v>0</v>
@@ -91574,7 +91574,7 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>5.653970270522433</v>
+        <v>0.9526475715196895</v>
       </c>
       <c r="JC114" t="n">
         <v>0</v>
@@ -92369,7 +92369,7 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.06608343730067928</v>
+        <v>1.996323785759845</v>
       </c>
       <c r="JC115" t="n">
         <v>0</v>
@@ -93164,7 +93164,7 @@
         <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>5.653970270522433</v>
+        <v>0.9526475715196895</v>
       </c>
       <c r="JC116" t="n">
         <v>0</v>
@@ -93959,7 +93959,7 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.06608343730067928</v>
+        <v>0.9526475715196895</v>
       </c>
       <c r="JC117" t="n">
         <v>0</v>
@@ -94747,14 +94747,14 @@
       </c>
       <c r="IZ118" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA118" t="n">
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.06608343730067928</v>
+        <v>-0.09102864272046574</v>
       </c>
       <c r="JC118" t="n">
         <v>0</v>
@@ -95549,7 +95549,7 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC119" t="n">
         <v>0</v>
@@ -96344,7 +96344,7 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC120" t="n">
         <v>0</v>
@@ -97132,14 +97132,14 @@
       </c>
       <c r="IZ121" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA121" t="n">
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.6660834373006792</v>
+        <v>0.7526475715196894</v>
       </c>
       <c r="JC121" t="n">
         <v>0</v>
@@ -97934,7 +97934,7 @@
         <v>1</v>
       </c>
       <c r="JB122" t="n">
-        <v>5.653970270522433</v>
+        <v>0.7526475715196894</v>
       </c>
       <c r="JC122" t="n">
         <v>0</v>
@@ -98729,7 +98729,7 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.06608343730067928</v>
+        <v>1.996323785759845</v>
       </c>
       <c r="JC123" t="n">
         <v>0</v>
@@ -99524,7 +99524,7 @@
         <v>1</v>
       </c>
       <c r="JB124" t="n">
-        <v>5.653970270522433</v>
+        <v>0.9526475715196895</v>
       </c>
       <c r="JC124" t="n">
         <v>0</v>
@@ -100319,7 +100319,7 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.06608343730067928</v>
+        <v>0.9526475715196895</v>
       </c>
       <c r="JC125" t="n">
         <v>0</v>
@@ -101107,14 +101107,14 @@
       </c>
       <c r="IZ126" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA126" t="n">
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.06608343730067928</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC126" t="n">
         <v>0</v>

--- a/out/Attention-Mamba1_repeat_4_000005.xlsx
+++ b/out/Attention-Mamba1_repeat_4_000005.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>-0.0009017530828714371</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.16</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>-0.0009583663195371628</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.16</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>-0.0008524078875780106</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.2910286427204658</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>-0.001069871708750725</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.2910286427204658</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>-0.001307213678956032</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.2910286427204658</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>-0.001289024949073792</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.2910286427204658</v>
+        <v>0.3</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>-0.001144932582974434</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>-0.001644102856516838</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>-0.001729704439640045</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9682,14 +9682,14 @@
       </c>
       <c r="IZ11" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>-0.001827934756875038</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10477,14 +10477,14 @@
       </c>
       <c r="IZ12" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>-0.001809002831578255</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11272,14 +11272,14 @@
       </c>
       <c r="IZ13" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>-0.00198819674551487</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>-0.002057148143649101</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>-0.002031901851296425</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>-0.002017034217715263</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>-0.001442676410079002</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.2910286427204658</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>-0.001325437799096107</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.2910286427204658</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>-0.0001932960003614426</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.2910286427204658</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>-0.001091683283448219</v>
       </c>
       <c r="JB20" t="n">
-        <v>0.9526475715196895</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>5.686469376087189e-05</v>
       </c>
       <c r="JB21" t="n">
-        <v>0.9526475715196895</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>-0.00077846460044384</v>
       </c>
       <c r="JB22" t="n">
-        <v>0.9526475715196895</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>-0.001654069870710373</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.09102864272046574</v>
+        <v>0.16</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>-0.001856518909335136</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.09102864272046574</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0</v>
+        <v>-0.001496413722634315</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>-0.002074459567666054</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>-0.00191672146320343</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>-0.001657405868172646</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>-0.00209314189851284</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>-0.00189780630171299</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>-0.001581268385052681</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.9526475715196895</v>
+        <v>0.16</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0.0005118567496538162</v>
       </c>
       <c r="JB32" t="n">
-        <v>0.9526475715196895</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>-0.00121043436229229</v>
       </c>
       <c r="JB33" t="n">
-        <v>0.9526475715196895</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>-0.001281855627894402</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.09102864272046574</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>-0.001638185232877731</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.09102864272046574</v>
+        <v>0.16</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>-0.001985149458050728</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>-0.001634666696190834</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>-0.002083567902445793</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>-0.002054844051599503</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>-0.00195041112601757</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>-0.001930100843310356</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34327,14 +34327,14 @@
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0</v>
+        <v>-0.001959081739187241</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35122,14 +35122,14 @@
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0</v>
+        <v>-0.002207258716225624</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35917,14 +35917,14 @@
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>0</v>
+        <v>-0.002253146842122078</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36712,14 +36712,14 @@
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0</v>
+        <v>-0.002055482938885689</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC45" t="n">
         <v>0</v>
@@ -37507,14 +37507,14 @@
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>-0.00223226472735405</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC46" t="n">
         <v>0</v>
@@ -38302,14 +38302,14 @@
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0</v>
+        <v>-0.00217905081808567</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC47" t="n">
         <v>0</v>
@@ -39097,14 +39097,14 @@
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>-0.002054283395409584</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC48" t="n">
         <v>0</v>
@@ -39892,14 +39892,14 @@
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>-0.0022475216537714</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC49" t="n">
         <v>0</v>
@@ -40687,14 +40687,14 @@
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>-0.002119811251759529</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC50" t="n">
         <v>0</v>
@@ -41482,14 +41482,14 @@
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>-0.002242131158709526</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC51" t="n">
         <v>0</v>
@@ -42277,14 +42277,14 @@
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>-0.002008860930800438</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC52" t="n">
         <v>0</v>
@@ -43076,10 +43076,10 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>-0.002148648723959923</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC53" t="n">
         <v>0</v>
@@ -43871,10 +43871,10 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>-0.002162782475352287</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC54" t="n">
         <v>0</v>
@@ -44666,10 +44666,10 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>-0.001894639804959297</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.2910286427204658</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC55" t="n">
         <v>0</v>
@@ -45461,10 +45461,10 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>-0.002124445512890816</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.2910286427204658</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC56" t="n">
         <v>0</v>
@@ -46256,10 +46256,10 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>-0.001400241628289223</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.2910286427204658</v>
+        <v>0.3</v>
       </c>
       <c r="JC57" t="n">
         <v>0</v>
@@ -47051,10 +47051,10 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>-0.00191180594265461</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.2910286427204658</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC58" t="n">
         <v>0</v>
@@ -47846,10 +47846,10 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0</v>
+        <v>-0.001767607405781746</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.2910286427204658</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC59" t="n">
         <v>0</v>
@@ -48641,10 +48641,10 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>-0.001809360459446907</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.2910286427204658</v>
+        <v>0.3</v>
       </c>
       <c r="JC60" t="n">
         <v>0</v>
@@ -49436,10 +49436,10 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>-0.00203593447804451</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.2910286427204658</v>
+        <v>0.3</v>
       </c>
       <c r="JC61" t="n">
         <v>0</v>
@@ -50231,10 +50231,10 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>-0.001864347606897354</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.2910286427204658</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC62" t="n">
         <v>0</v>
@@ -51022,14 +51022,14 @@
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>-0.002342579886317253</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC63" t="n">
         <v>0</v>
@@ -51817,14 +51817,14 @@
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>-0.002266893163323402</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC64" t="n">
         <v>0</v>
@@ -52612,14 +52612,14 @@
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0</v>
+        <v>-0.002374971285462379</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC65" t="n">
         <v>0</v>
@@ -53407,14 +53407,14 @@
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>-0.002478079870343208</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC66" t="n">
         <v>0</v>
@@ -54202,14 +54202,14 @@
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0</v>
+        <v>-0.002207813784480095</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC67" t="n">
         <v>0</v>
@@ -54997,14 +54997,14 @@
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>-0.002339830622076988</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC68" t="n">
         <v>0</v>
@@ -55792,14 +55792,14 @@
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>-0.002352626994252205</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC69" t="n">
         <v>0</v>
@@ -56587,14 +56587,14 @@
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>-0.002185424789786339</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC70" t="n">
         <v>0</v>
@@ -57382,14 +57382,14 @@
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>-0.002286346629261971</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
         <v>0</v>
@@ -58181,10 +58181,10 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>-0.002664772793650627</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC72" t="n">
         <v>0</v>
@@ -58976,10 +58976,10 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>-0.00235828198492527</v>
       </c>
       <c r="JB73" t="n">
-        <v>0.9526475715196895</v>
+        <v>0.16</v>
       </c>
       <c r="JC73" t="n">
         <v>0</v>
@@ -59771,10 +59771,10 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0.0001456830650568008</v>
       </c>
       <c r="JB74" t="n">
-        <v>0.9526475715196895</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC74" t="n">
         <v>0</v>
@@ -60566,10 +60566,10 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>-0.00154532864689827</v>
       </c>
       <c r="JB75" t="n">
-        <v>1.996323785759845</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC75" t="n">
         <v>0</v>
@@ -61361,10 +61361,10 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0.0003777574747800827</v>
       </c>
       <c r="JB76" t="n">
-        <v>0.9526475715196895</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC76" t="n">
         <v>0</v>
@@ -62156,10 +62156,10 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>-0.0009365733712911606</v>
       </c>
       <c r="JB77" t="n">
-        <v>0.9526475715196895</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC77" t="n">
         <v>0</v>
@@ -62947,14 +62947,14 @@
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>-0.0009355377405881882</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.09102864272046574</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC78" t="n">
         <v>0</v>
@@ -63746,10 +63746,10 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>-0.001398185268044472</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.2910286427204658</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC79" t="n">
         <v>0</v>
@@ -64541,10 +64541,10 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>-0.001507218927145004</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.2910286427204658</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC80" t="n">
         <v>0</v>
@@ -65336,10 +65336,10 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>-0.00169903039932251</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.2910286427204658</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC81" t="n">
         <v>0</v>
@@ -66131,10 +66131,10 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>-0.001761374995112419</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.3</v>
       </c>
       <c r="JC82" t="n">
         <v>0</v>
@@ -66926,10 +66926,10 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>-0.001309426501393318</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.3</v>
       </c>
       <c r="JC83" t="n">
         <v>0</v>
@@ -67717,14 +67717,14 @@
       </c>
       <c r="IZ84" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>-0.002341853454709053</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC84" t="n">
         <v>0</v>
@@ -68512,14 +68512,14 @@
       </c>
       <c r="IZ85" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>-0.001433880999684334</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC85" t="n">
         <v>0</v>
@@ -69307,14 +69307,14 @@
       </c>
       <c r="IZ86" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>-0.001914376392960548</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC86" t="n">
         <v>0</v>
@@ -70106,10 +70106,10 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>-0.002231191843748093</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC87" t="n">
         <v>0</v>
@@ -70901,10 +70901,10 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>-0.0001286156475543976</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.3</v>
       </c>
       <c r="JC88" t="n">
         <v>0</v>
@@ -71696,10 +71696,10 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>-0.001412751153111458</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.2910286427204658</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC89" t="n">
         <v>0</v>
@@ -72491,10 +72491,10 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>-0.001622738316655159</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.2910286427204658</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC90" t="n">
         <v>0</v>
@@ -73286,10 +73286,10 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>-0.001668931916356087</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.2910286427204658</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC91" t="n">
         <v>0</v>
@@ -74081,10 +74081,10 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>-0.001608302816748619</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.2910286427204658</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC92" t="n">
         <v>0</v>
@@ -74872,14 +74872,14 @@
       </c>
       <c r="IZ93" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>-0.002050651237368584</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC93" t="n">
         <v>0</v>
@@ -75667,14 +75667,14 @@
       </c>
       <c r="IZ94" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>-0.002194402739405632</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC94" t="n">
         <v>0</v>
@@ -76462,14 +76462,14 @@
       </c>
       <c r="IZ95" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>-0.001774942502379417</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC95" t="n">
         <v>0</v>
@@ -77257,14 +77257,14 @@
       </c>
       <c r="IZ96" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>-0.001526897773146629</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC96" t="n">
         <v>0</v>
@@ -78052,14 +78052,14 @@
       </c>
       <c r="IZ97" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>-0.001957910135388374</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC97" t="n">
         <v>0</v>
@@ -78847,14 +78847,14 @@
       </c>
       <c r="IZ98" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>-0.001783782616257668</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC98" t="n">
         <v>0</v>
@@ -79642,14 +79642,14 @@
       </c>
       <c r="IZ99" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>-0.001782501116394997</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC99" t="n">
         <v>0</v>
@@ -80437,14 +80437,14 @@
       </c>
       <c r="IZ100" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>-0.002174505963921547</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC100" t="n">
         <v>0</v>
@@ -81236,10 +81236,10 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>-0.001814642921090126</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC101" t="n">
         <v>0</v>
@@ -82031,10 +82031,10 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>-0.001484610140323639</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC102" t="n">
         <v>0</v>
@@ -82826,10 +82826,10 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>-0.001993576064705849</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC103" t="n">
         <v>0</v>
@@ -83617,14 +83617,14 @@
       </c>
       <c r="IZ104" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>-0.001747244969010353</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.2910286427204658</v>
+        <v>0.3</v>
       </c>
       <c r="JC104" t="n">
         <v>0</v>
@@ -84412,14 +84412,14 @@
       </c>
       <c r="IZ105" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>-0.001355819404125214</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.2910286427204658</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC105" t="n">
         <v>0</v>
@@ -85207,14 +85207,14 @@
       </c>
       <c r="IZ106" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>-0.001464042812585831</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.2910286427204658</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC106" t="n">
         <v>0</v>
@@ -86002,14 +86002,14 @@
       </c>
       <c r="IZ107" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>-0.002138081938028336</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.2910286427204658</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC107" t="n">
         <v>0</v>
@@ -86797,14 +86797,14 @@
       </c>
       <c r="IZ108" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>-0.001435386016964912</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.2910286427204658</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC108" t="n">
         <v>0</v>
@@ -87592,14 +87592,14 @@
       </c>
       <c r="IZ109" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>-0.002196641638875008</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC109" t="n">
         <v>0</v>
@@ -88391,10 +88391,10 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>-0.002302035689353943</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC110" t="n">
         <v>0</v>
@@ -89186,10 +89186,10 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>-0.002871779724955559</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC111" t="n">
         <v>0</v>
@@ -89981,10 +89981,10 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>-0.003037551417946815</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC112" t="n">
         <v>0</v>
@@ -90772,14 +90772,14 @@
       </c>
       <c r="IZ113" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>-0.003206536173820496</v>
       </c>
       <c r="JB113" t="n">
-        <v>0.9526475715196895</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC113" t="n">
         <v>0</v>
@@ -91567,14 +91567,14 @@
       </c>
       <c r="IZ114" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0.0005758609622716904</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.9526475715196895</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC114" t="n">
         <v>0</v>
@@ -92366,10 +92366,10 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>-0.004158006981015205</v>
       </c>
       <c r="JB115" t="n">
-        <v>1.996323785759845</v>
+        <v>0.16</v>
       </c>
       <c r="JC115" t="n">
         <v>0</v>
@@ -93161,10 +93161,10 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0.001564079895615578</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.9526475715196895</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC116" t="n">
         <v>0</v>
@@ -93956,10 +93956,10 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>-0.002006186172366142</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.9526475715196895</v>
+        <v>0.3</v>
       </c>
       <c r="JC117" t="n">
         <v>0</v>
@@ -94747,14 +94747,14 @@
       </c>
       <c r="IZ118" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>-0.0007966756820678711</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.09102864272046574</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC118" t="n">
         <v>0</v>
@@ -95542,14 +95542,14 @@
       </c>
       <c r="IZ119" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>-0.001164337620139122</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.2910286427204658</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC119" t="n">
         <v>0</v>
@@ -96337,14 +96337,14 @@
       </c>
       <c r="IZ120" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>-0.001669721677899361</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.2910286427204658</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC120" t="n">
         <v>0</v>
@@ -97136,10 +97136,10 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>-0.001132264733314514</v>
       </c>
       <c r="JB121" t="n">
-        <v>0.7526475715196894</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC121" t="n">
         <v>0</v>
@@ -97931,10 +97931,10 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0.002063436433672905</v>
       </c>
       <c r="JB122" t="n">
-        <v>0.7526475715196894</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC122" t="n">
         <v>0</v>
@@ -98726,10 +98726,10 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>-0.0006845183670520782</v>
       </c>
       <c r="JB123" t="n">
-        <v>1.996323785759845</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC123" t="n">
         <v>0</v>
@@ -99521,10 +99521,10 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0.001839198172092438</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.9526475715196895</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC124" t="n">
         <v>0</v>
@@ -100316,10 +100316,10 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>-0.002062888815999031</v>
       </c>
       <c r="JB125" t="n">
-        <v>0.9526475715196895</v>
+        <v>0.5799999999999997</v>
       </c>
       <c r="JC125" t="n">
         <v>0</v>
@@ -101107,14 +101107,14 @@
       </c>
       <c r="IZ126" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>-0.0008442234247922897</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.1600000000000003</v>
       </c>
       <c r="JC126" t="n">
         <v>0</v>

--- a/out/Attention-Mamba1_repeat_4_000005.xlsx
+++ b/out/Attention-Mamba1_repeat_4_000005.xlsx
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>-0.0009017530828714371</v>
+        <v>-0.0009017549455165863</v>
       </c>
       <c r="JB2" t="n">
         <v>-0.16</v>
@@ -3326,7 +3326,7 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>-0.0009583663195371628</v>
+        <v>-0.0009583793580532074</v>
       </c>
       <c r="JB3" t="n">
         <v>-0.16</v>
@@ -4121,7 +4121,7 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>-0.0008524078875780106</v>
+        <v>-0.0008523818105459213</v>
       </c>
       <c r="JB4" t="n">
         <v>0.4399999999999999</v>
@@ -4916,7 +4916,7 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>-0.001069871708750725</v>
+        <v>-0.001069854944944382</v>
       </c>
       <c r="JB5" t="n">
         <v>0.4399999999999999</v>
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>-0.001307213678956032</v>
+        <v>-0.001307226717472076</v>
       </c>
       <c r="JB6" t="n">
         <v>0.4399999999999999</v>
@@ -6506,7 +6506,7 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>-0.001289024949073792</v>
+        <v>-0.001289023086428642</v>
       </c>
       <c r="JB7" t="n">
         <v>0.3</v>
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>-0.001144932582974434</v>
+        <v>-0.001144936308264732</v>
       </c>
       <c r="JB8" t="n">
         <v>-0.4399999999999999</v>
@@ -8096,7 +8096,7 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>-0.001644102856516838</v>
+        <v>-0.001644128933548927</v>
       </c>
       <c r="JB9" t="n">
         <v>-0.5799999999999998</v>
@@ -8891,7 +8891,7 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>-0.001729704439640045</v>
+        <v>-0.001729685813188553</v>
       </c>
       <c r="JB10" t="n">
         <v>-0.7199999999999999</v>
@@ -9686,7 +9686,7 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>-0.001827934756875038</v>
+        <v>-0.001827927306294441</v>
       </c>
       <c r="JB11" t="n">
         <v>-0.8599999999999999</v>
@@ -10481,7 +10481,7 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>-0.001809002831578255</v>
+        <v>-0.00180901400744915</v>
       </c>
       <c r="JB12" t="n">
         <v>-0.9999999999999998</v>
@@ -11276,7 +11276,7 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>-0.00198819674551487</v>
+        <v>-0.001988185569643974</v>
       </c>
       <c r="JB13" t="n">
         <v>-0.9999999999999998</v>
@@ -12071,7 +12071,7 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>-0.002057148143649101</v>
+        <v>-0.0020571518689394</v>
       </c>
       <c r="JB14" t="n">
         <v>-0.9999999999999998</v>
@@ -12866,7 +12866,7 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>-0.002031901851296425</v>
+        <v>-0.002031886950135231</v>
       </c>
       <c r="JB15" t="n">
         <v>-0.7199999999999999</v>
@@ -13661,7 +13661,7 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>-0.002017034217715263</v>
+        <v>-0.00201704166829586</v>
       </c>
       <c r="JB16" t="n">
         <v>-0.4399999999999999</v>
@@ -14456,7 +14456,7 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>-0.001442676410079002</v>
+        <v>-0.001442668959498405</v>
       </c>
       <c r="JB17" t="n">
         <v>0.4399999999999999</v>
@@ -15251,7 +15251,7 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>-0.001325437799096107</v>
+        <v>-0.001325441524386406</v>
       </c>
       <c r="JB18" t="n">
         <v>0.7199999999999999</v>
@@ -16046,7 +16046,7 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>-0.0001932960003614426</v>
+        <v>-0.0001933109015226364</v>
       </c>
       <c r="JB19" t="n">
         <v>0.9999999999999998</v>
@@ -17636,7 +17636,7 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>5.686469376087189e-05</v>
+        <v>5.68535178899765e-05</v>
       </c>
       <c r="JB21" t="n">
         <v>0.7199999999999999</v>
@@ -18431,7 +18431,7 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>-0.00077846460044384</v>
+        <v>-0.0007784981280565262</v>
       </c>
       <c r="JB22" t="n">
         <v>0.4399999999999999</v>
@@ -19226,7 +19226,7 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>-0.001654069870710373</v>
+        <v>-0.001654064282774925</v>
       </c>
       <c r="JB23" t="n">
         <v>0.16</v>
@@ -20021,7 +20021,7 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>-0.001856518909335136</v>
+        <v>-0.001856507733464241</v>
       </c>
       <c r="JB24" t="n">
         <v>-0.7199999999999999</v>
@@ -20816,7 +20816,7 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>-0.001496413722634315</v>
+        <v>-0.001496395096182823</v>
       </c>
       <c r="JB25" t="n">
         <v>-0.9999999999999998</v>
@@ -21611,7 +21611,7 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>-0.002074459567666054</v>
+        <v>-0.002074446529150009</v>
       </c>
       <c r="JB26" t="n">
         <v>-0.9999999999999998</v>
@@ -22406,7 +22406,7 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>-0.00191672146320343</v>
+        <v>-0.001916700974106789</v>
       </c>
       <c r="JB27" t="n">
         <v>-0.9999999999999998</v>
@@ -23201,7 +23201,7 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>-0.001657405868172646</v>
+        <v>-0.001657400280237198</v>
       </c>
       <c r="JB28" t="n">
         <v>-0.9999999999999998</v>
@@ -23996,7 +23996,7 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>-0.00209314189851284</v>
+        <v>-0.002093125134706497</v>
       </c>
       <c r="JB29" t="n">
         <v>-0.9999999999999998</v>
@@ -24791,7 +24791,7 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>-0.00189780630171299</v>
+        <v>-0.001897802576422691</v>
       </c>
       <c r="JB30" t="n">
         <v>-0.7199999999999999</v>
@@ -25586,7 +25586,7 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>-0.001581268385052681</v>
+        <v>-0.001581279560923576</v>
       </c>
       <c r="JB31" t="n">
         <v>0.16</v>
@@ -26381,7 +26381,7 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0.0005118567496538162</v>
+        <v>0.0005118530243635178</v>
       </c>
       <c r="JB32" t="n">
         <v>0.4399999999999999</v>
@@ -27176,7 +27176,7 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>-0.00121043436229229</v>
+        <v>-0.001210426911711693</v>
       </c>
       <c r="JB33" t="n">
         <v>0.4399999999999999</v>
@@ -27971,7 +27971,7 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>-0.001281855627894402</v>
+        <v>-0.001281885430216789</v>
       </c>
       <c r="JB34" t="n">
         <v>0.4399999999999999</v>
@@ -28766,7 +28766,7 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>-0.001638185232877731</v>
+        <v>-0.001638183370232582</v>
       </c>
       <c r="JB35" t="n">
         <v>0.16</v>
@@ -29561,7 +29561,7 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>-0.001985149458050728</v>
+        <v>-0.001985145732760429</v>
       </c>
       <c r="JB36" t="n">
         <v>-0.1199999999999999</v>
@@ -30356,7 +30356,7 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>-0.001634666696190834</v>
+        <v>-0.001634674146771431</v>
       </c>
       <c r="JB37" t="n">
         <v>-0.9999999999999998</v>
@@ -31151,7 +31151,7 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>-0.002083567902445793</v>
+        <v>-0.002083554863929749</v>
       </c>
       <c r="JB38" t="n">
         <v>-0.9999999999999998</v>
@@ -31946,7 +31946,7 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>-0.002054844051599503</v>
+        <v>-0.002054829150438309</v>
       </c>
       <c r="JB39" t="n">
         <v>-0.9999999999999998</v>
@@ -32741,7 +32741,7 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>-0.00195041112601757</v>
+        <v>-0.001950418576598167</v>
       </c>
       <c r="JB40" t="n">
         <v>-0.9999999999999998</v>
@@ -33536,7 +33536,7 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>-0.001930100843310356</v>
+        <v>-0.001930080354213715</v>
       </c>
       <c r="JB41" t="n">
         <v>-0.9999999999999998</v>
@@ -34331,7 +34331,7 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>-0.001959081739187241</v>
+        <v>-0.001959076151251793</v>
       </c>
       <c r="JB42" t="n">
         <v>-0.9999999999999998</v>
@@ -35126,7 +35126,7 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>-0.002207258716225624</v>
+        <v>-0.002207277342677116</v>
       </c>
       <c r="JB43" t="n">
         <v>-0.9999999999999998</v>
@@ -35921,7 +35921,7 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>-0.002253146842122078</v>
+        <v>-0.002253124490380287</v>
       </c>
       <c r="JB44" t="n">
         <v>-0.9999999999999998</v>
@@ -36716,7 +36716,7 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>-0.002055482938885689</v>
+        <v>-0.00205550529062748</v>
       </c>
       <c r="JB45" t="n">
         <v>-0.9999999999999998</v>
@@ -37511,7 +37511,7 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>-0.00223226472735405</v>
+        <v>-0.002232281491160393</v>
       </c>
       <c r="JB46" t="n">
         <v>-0.9999999999999998</v>
@@ -38306,7 +38306,7 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>-0.00217905081808567</v>
+        <v>-0.002179069444537163</v>
       </c>
       <c r="JB47" t="n">
         <v>-0.9999999999999998</v>
@@ -39101,7 +39101,7 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>-0.002054283395409584</v>
+        <v>-0.002054270356893539</v>
       </c>
       <c r="JB48" t="n">
         <v>-0.9999999999999998</v>
@@ -39896,7 +39896,7 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>-0.0022475216537714</v>
+        <v>-0.002247514203190804</v>
       </c>
       <c r="JB49" t="n">
         <v>-0.9999999999999998</v>
@@ -40691,7 +40691,7 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>-0.002119811251759529</v>
+        <v>-0.002119824290275574</v>
       </c>
       <c r="JB50" t="n">
         <v>-0.9999999999999998</v>
@@ -41486,7 +41486,7 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>-0.002242131158709526</v>
+        <v>-0.002242119982838631</v>
       </c>
       <c r="JB51" t="n">
         <v>-0.9999999999999998</v>
@@ -42281,7 +42281,7 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>-0.002008860930800438</v>
+        <v>-0.002008853480219841</v>
       </c>
       <c r="JB52" t="n">
         <v>-0.9999999999999998</v>
@@ -43076,7 +43076,7 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>-0.002148648723959923</v>
+        <v>-0.002148594707250595</v>
       </c>
       <c r="JB53" t="n">
         <v>-0.2599999999999998</v>
@@ -43871,7 +43871,7 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>-0.002162782475352287</v>
+        <v>-0.002162786200642586</v>
       </c>
       <c r="JB54" t="n">
         <v>-0.2599999999999998</v>
@@ -44666,7 +44666,7 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>-0.001894639804959297</v>
+        <v>-0.001894647255539894</v>
       </c>
       <c r="JB55" t="n">
         <v>0.02000000000000007</v>
@@ -45461,7 +45461,7 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>-0.002124445512890816</v>
+        <v>-0.002124430611729622</v>
       </c>
       <c r="JB56" t="n">
         <v>0.02000000000000007</v>
@@ -46256,7 +46256,7 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>-0.001400241628289223</v>
+        <v>-0.001400262117385864</v>
       </c>
       <c r="JB57" t="n">
         <v>0.3</v>
@@ -47051,7 +47051,7 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>-0.00191180594265461</v>
+        <v>-0.001911820843815804</v>
       </c>
       <c r="JB58" t="n">
         <v>0.4399999999999999</v>
@@ -47846,7 +47846,7 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>-0.001767607405781746</v>
+        <v>-0.001767570152878761</v>
       </c>
       <c r="JB59" t="n">
         <v>0.4399999999999999</v>
@@ -48641,7 +48641,7 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>-0.001809360459446907</v>
+        <v>-0.001809375360608101</v>
       </c>
       <c r="JB60" t="n">
         <v>0.3</v>
@@ -49436,7 +49436,7 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>-0.00203593447804451</v>
+        <v>-0.002035947516560555</v>
       </c>
       <c r="JB61" t="n">
         <v>0.3</v>
@@ -50231,7 +50231,7 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>-0.001864347606897354</v>
+        <v>-0.001864345744252205</v>
       </c>
       <c r="JB62" t="n">
         <v>0.02000000000000007</v>
@@ -51026,7 +51026,7 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>-0.002342579886317253</v>
+        <v>-0.002342583611607552</v>
       </c>
       <c r="JB63" t="n">
         <v>-0.8599999999999999</v>
@@ -51821,7 +51821,7 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>-0.002266893163323402</v>
+        <v>-0.002266904339194298</v>
       </c>
       <c r="JB64" t="n">
         <v>-0.8599999999999999</v>
@@ -53411,7 +53411,7 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>-0.002478079870343208</v>
+        <v>-0.002478063106536865</v>
       </c>
       <c r="JB66" t="n">
         <v>-0.9999999999999998</v>
@@ -54206,7 +54206,7 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>-0.002207813784480095</v>
+        <v>-0.002207823097705841</v>
       </c>
       <c r="JB67" t="n">
         <v>-0.9999999999999998</v>
@@ -55001,7 +55001,7 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>-0.002339830622076988</v>
+        <v>-0.002339836210012436</v>
       </c>
       <c r="JB68" t="n">
         <v>-0.9999999999999998</v>
@@ -55796,7 +55796,7 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>-0.002352626994252205</v>
+        <v>-0.0023526381701231</v>
       </c>
       <c r="JB69" t="n">
         <v>-0.9999999999999998</v>
@@ -56591,7 +56591,7 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>-0.002185424789786339</v>
+        <v>-0.00218544714152813</v>
       </c>
       <c r="JB70" t="n">
         <v>-0.9999999999999998</v>
@@ -58181,7 +58181,7 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>-0.002664772793650627</v>
+        <v>-0.002664750441908836</v>
       </c>
       <c r="JB72" t="n">
         <v>-0.1199999999999999</v>
@@ -58976,7 +58976,7 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>-0.00235828198492527</v>
+        <v>-0.002358278259634972</v>
       </c>
       <c r="JB73" t="n">
         <v>0.16</v>
@@ -59771,7 +59771,7 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0.0001456830650568008</v>
+        <v>0.0001456905156373978</v>
       </c>
       <c r="JB74" t="n">
         <v>0.4399999999999999</v>
@@ -60566,7 +60566,7 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>-0.00154532864689827</v>
+        <v>-0.001545343548059464</v>
       </c>
       <c r="JB75" t="n">
         <v>0.7199999999999999</v>
@@ -61361,7 +61361,7 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0.0003777574747800827</v>
+        <v>0.0003777686506509781</v>
       </c>
       <c r="JB76" t="n">
         <v>0.9999999999999998</v>
@@ -62156,7 +62156,7 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>-0.0009365733712911606</v>
+        <v>-0.0009365435689687729</v>
       </c>
       <c r="JB77" t="n">
         <v>0.8599999999999999</v>
@@ -62951,7 +62951,7 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>-0.0009355377405881882</v>
+        <v>-0.0009355451911687851</v>
       </c>
       <c r="JB78" t="n">
         <v>0.8599999999999999</v>
@@ -63746,7 +63746,7 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>-0.001398185268044472</v>
+        <v>-0.001398192718625069</v>
       </c>
       <c r="JB79" t="n">
         <v>0.7199999999999999</v>
@@ -64541,7 +64541,7 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>-0.001507218927145004</v>
+        <v>-0.001507190987467766</v>
       </c>
       <c r="JB80" t="n">
         <v>0.5799999999999998</v>
@@ -65336,7 +65336,7 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>-0.00169903039932251</v>
+        <v>-0.001699026674032211</v>
       </c>
       <c r="JB81" t="n">
         <v>0.4399999999999999</v>
@@ -66131,7 +66131,7 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>-0.001761374995112419</v>
+        <v>-0.001761369407176971</v>
       </c>
       <c r="JB82" t="n">
         <v>-0.3</v>
@@ -66926,7 +66926,7 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>-0.001309426501393318</v>
+        <v>-0.001309406012296677</v>
       </c>
       <c r="JB83" t="n">
         <v>-0.3</v>
@@ -67721,7 +67721,7 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>-0.002341853454709053</v>
+        <v>-0.002341842278838158</v>
       </c>
       <c r="JB84" t="n">
         <v>-0.4399999999999999</v>
@@ -68516,7 +68516,7 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>-0.001433880999684334</v>
+        <v>-0.001433879137039185</v>
       </c>
       <c r="JB85" t="n">
         <v>-0.5799999999999998</v>
@@ -69311,7 +69311,7 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>-0.001914376392960548</v>
+        <v>-0.001914383843541145</v>
       </c>
       <c r="JB86" t="n">
         <v>-0.4399999999999999</v>
@@ -70106,7 +70106,7 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>-0.002231191843748093</v>
+        <v>-0.002231186255812645</v>
       </c>
       <c r="JB87" t="n">
         <v>-0.1600000000000001</v>
@@ -70901,7 +70901,7 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>-0.0001286156475543976</v>
+        <v>-0.0001286361366510391</v>
       </c>
       <c r="JB88" t="n">
         <v>-0.3</v>
@@ -71696,7 +71696,7 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>-0.001412751153111458</v>
+        <v>-0.001412762328982353</v>
       </c>
       <c r="JB89" t="n">
         <v>0.4399999999999999</v>
@@ -72491,7 +72491,7 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>-0.001622738316655159</v>
+        <v>-0.001622732728719711</v>
       </c>
       <c r="JB90" t="n">
         <v>0.7199999999999999</v>
@@ -73286,7 +73286,7 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>-0.001668931916356087</v>
+        <v>-0.001668928191065788</v>
       </c>
       <c r="JB91" t="n">
         <v>0.4399999999999999</v>
@@ -74081,7 +74081,7 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>-0.001608302816748619</v>
+        <v>-0.001608310267329216</v>
       </c>
       <c r="JB92" t="n">
         <v>0.1600000000000001</v>
@@ -74876,7 +74876,7 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>-0.002050651237368584</v>
+        <v>-0.002050647512078285</v>
       </c>
       <c r="JB93" t="n">
         <v>-0.5799999999999998</v>
@@ -75671,7 +75671,7 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>-0.002194402739405632</v>
+        <v>-0.002194399014115334</v>
       </c>
       <c r="JB94" t="n">
         <v>-0.4399999999999999</v>
@@ -76466,7 +76466,7 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>-0.001774942502379417</v>
+        <v>-0.001774933189153671</v>
       </c>
       <c r="JB95" t="n">
         <v>-0.7199999999999999</v>
@@ -77261,7 +77261,7 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>-0.001526897773146629</v>
+        <v>-0.001526894047856331</v>
       </c>
       <c r="JB96" t="n">
         <v>-0.7199999999999999</v>
@@ -78056,7 +78056,7 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>-0.001957910135388374</v>
+        <v>-0.001957925036549568</v>
       </c>
       <c r="JB97" t="n">
         <v>-0.7199999999999999</v>
@@ -78851,7 +78851,7 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>-0.001783782616257668</v>
+        <v>-0.001783793792128563</v>
       </c>
       <c r="JB98" t="n">
         <v>-0.7199999999999999</v>
@@ -79646,7 +79646,7 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>-0.001782501116394997</v>
+        <v>-0.001782508566975594</v>
       </c>
       <c r="JB99" t="n">
         <v>-0.9999999999999998</v>
@@ -80441,7 +80441,7 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>-0.002174505963921547</v>
+        <v>-0.002174517139792442</v>
       </c>
       <c r="JB100" t="n">
         <v>-0.8599999999999999</v>
@@ -82031,7 +82031,7 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>-0.001484610140323639</v>
+        <v>-0.001484626904129982</v>
       </c>
       <c r="JB102" t="n">
         <v>-0.8599999999999999</v>
@@ -82826,7 +82826,7 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>-0.001993576064705849</v>
+        <v>-0.001993568614125252</v>
       </c>
       <c r="JB103" t="n">
         <v>-0.5799999999999998</v>
@@ -83621,7 +83621,7 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>-0.001747244969010353</v>
+        <v>-0.001747267320752144</v>
       </c>
       <c r="JB104" t="n">
         <v>0.3</v>
@@ -84416,7 +84416,7 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>-0.001355819404125214</v>
+        <v>-0.001355802640318871</v>
       </c>
       <c r="JB105" t="n">
         <v>0.1600000000000001</v>
@@ -85211,7 +85211,7 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>-0.001464042812585831</v>
+        <v>-0.001464040949940681</v>
       </c>
       <c r="JB106" t="n">
         <v>0.4399999999999999</v>
@@ -86006,7 +86006,7 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>-0.002138081938028336</v>
+        <v>-0.002138076350092888</v>
       </c>
       <c r="JB107" t="n">
         <v>0.4399999999999999</v>
@@ -86801,7 +86801,7 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>-0.001435386016964912</v>
+        <v>-0.001435408368706703</v>
       </c>
       <c r="JB108" t="n">
         <v>0.1600000000000001</v>
@@ -87596,7 +87596,7 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>-0.002196641638875008</v>
+        <v>-0.002196615561842918</v>
       </c>
       <c r="JB109" t="n">
         <v>-0.1199999999999999</v>
@@ -88391,7 +88391,7 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>-0.002302035689353943</v>
+        <v>-0.002302031964063644</v>
       </c>
       <c r="JB110" t="n">
         <v>-0.7199999999999999</v>
@@ -89186,7 +89186,7 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>-0.002871779724955559</v>
+        <v>-0.002871798351407051</v>
       </c>
       <c r="JB111" t="n">
         <v>-0.9999999999999998</v>
@@ -89981,7 +89981,7 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>-0.003037551417946815</v>
+        <v>-0.003037570044398308</v>
       </c>
       <c r="JB112" t="n">
         <v>-0.7199999999999999</v>
@@ -90776,7 +90776,7 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>-0.003206536173820496</v>
+        <v>-0.003206534311175346</v>
       </c>
       <c r="JB113" t="n">
         <v>-0.7199999999999999</v>
@@ -91571,7 +91571,7 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0.0005758609622716904</v>
+        <v>0.0005758572369813919</v>
       </c>
       <c r="JB114" t="n">
         <v>-0.4399999999999999</v>
@@ -92366,7 +92366,7 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>-0.004158006981015205</v>
+        <v>-0.004158036783337593</v>
       </c>
       <c r="JB115" t="n">
         <v>0.16</v>
@@ -93956,7 +93956,7 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>-0.002006186172366142</v>
+        <v>-0.002006193622946739</v>
       </c>
       <c r="JB117" t="n">
         <v>0.3</v>
@@ -94751,7 +94751,7 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>-0.0007966756820678711</v>
+        <v>-0.0007966775447130203</v>
       </c>
       <c r="JB118" t="n">
         <v>0.5799999999999998</v>
@@ -95546,7 +95546,7 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>-0.001164337620139122</v>
+        <v>-0.001164332032203674</v>
       </c>
       <c r="JB119" t="n">
         <v>0.4399999999999999</v>
@@ -96341,7 +96341,7 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>-0.001669721677899361</v>
+        <v>-0.001669725403189659</v>
       </c>
       <c r="JB120" t="n">
         <v>0.7199999999999999</v>
@@ -97136,7 +97136,7 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>-0.001132264733314514</v>
+        <v>-0.001132279634475708</v>
       </c>
       <c r="JB121" t="n">
         <v>0.7199999999999999</v>
@@ -97931,7 +97931,7 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0.002063436433672905</v>
+        <v>0.002063428983092308</v>
       </c>
       <c r="JB122" t="n">
         <v>0.8599999999999999</v>
@@ -98726,7 +98726,7 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>-0.0006845183670520782</v>
+        <v>-0.0006844978779554367</v>
       </c>
       <c r="JB123" t="n">
         <v>0.5799999999999998</v>
@@ -99521,7 +99521,7 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0.001839198172092438</v>
+        <v>0.001839214935898781</v>
       </c>
       <c r="JB124" t="n">
         <v>0.7199999999999999</v>
@@ -100316,7 +100316,7 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>-0.002062888815999031</v>
+        <v>-0.002062886953353882</v>
       </c>
       <c r="JB125" t="n">
         <v>0.5799999999999997</v>
@@ -101111,7 +101111,7 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>-0.0008442234247922897</v>
+        <v>-0.0008442159742116928</v>
       </c>
       <c r="JB126" t="n">
         <v>-0.1600000000000003</v>
